--- a/output/roomself_excel/14503.xlsx
+++ b/output/roomself_excel/14503.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29070</v>
+        <v>165052</v>
       </c>
       <c r="D2" t="n">
-        <v>1548</v>
+        <v>3504</v>
       </c>
       <c r="E2" t="n">
-        <v>323</v>
+        <v>598</v>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>99281</v>
+        <v>343039</v>
       </c>
       <c r="D3" t="n">
-        <v>2656</v>
+        <v>5601</v>
       </c>
       <c r="E3" t="n">
-        <v>620</v>
+        <v>667</v>
       </c>
       <c r="F3" t="n">
-        <v>155</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>104542</v>
+        <v>47328</v>
       </c>
       <c r="D5" t="n">
-        <v>2668</v>
+        <v>1744</v>
       </c>
       <c r="E5" t="n">
-        <v>493</v>
+        <v>204</v>
       </c>
       <c r="F5" t="n">
-        <v>437</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>199156</v>
+        <v>23691</v>
       </c>
       <c r="D6" t="n">
-        <v>4484</v>
+        <v>1232</v>
       </c>
       <c r="E6" t="n">
-        <v>703</v>
+        <v>133</v>
       </c>
       <c r="F6" t="n">
-        <v>471</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88564</v>
+        <v>102212</v>
       </c>
       <c r="D7" t="n">
-        <v>2584</v>
+        <v>3796</v>
       </c>
       <c r="E7" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>47328</v>
+        <v>67812</v>
       </c>
       <c r="D8" t="n">
-        <v>1744</v>
+        <v>2184</v>
       </c>
       <c r="E8" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48488</v>
+        <v>30814</v>
       </c>
       <c r="D9" t="n">
-        <v>1764</v>
+        <v>1436</v>
       </c>
       <c r="E9" t="n">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="F9" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>109440</v>
+        <v>29070</v>
       </c>
       <c r="D10" t="n">
-        <v>2676</v>
+        <v>1548</v>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23691</v>
+        <v>113685</v>
       </c>
       <c r="D11" t="n">
-        <v>1232</v>
+        <v>2776</v>
       </c>
       <c r="E11" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>165052</v>
+        <v>37264</v>
       </c>
       <c r="D12" t="n">
-        <v>3504</v>
+        <v>1640</v>
       </c>
       <c r="E12" t="n">
-        <v>598</v>
+        <v>287</v>
       </c>
       <c r="F12" t="n">
-        <v>367</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>439416</v>
+        <v>178125</v>
       </c>
       <c r="D13" t="n">
-        <v>5320</v>
+        <v>3070</v>
       </c>
       <c r="E13" t="n">
-        <v>755</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>113685</v>
+        <v>99281</v>
       </c>
       <c r="D14" t="n">
-        <v>2776</v>
+        <v>2656</v>
       </c>
       <c r="E14" t="n">
         <v>284</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10707</v>
+        <v>104542</v>
       </c>
       <c r="D15" t="n">
-        <v>848</v>
+        <v>2668</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>513063</v>
+        <v>199156</v>
       </c>
       <c r="D16" t="n">
-        <v>10612</v>
+        <v>4484</v>
       </c>
       <c r="E16" t="n">
-        <v>1179</v>
+        <v>586</v>
       </c>
       <c r="F16" t="n">
-        <v>980</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>122455</v>
+        <v>88564</v>
       </c>
       <c r="D17" t="n">
-        <v>3032</v>
+        <v>2584</v>
       </c>
       <c r="E17" t="n">
-        <v>538</v>
+        <v>304</v>
       </c>
       <c r="F17" t="n">
-        <v>299</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>346760</v>
+        <v>48488</v>
       </c>
       <c r="D18" t="n">
-        <v>5472</v>
+        <v>1764</v>
       </c>
       <c r="E18" t="n">
-        <v>685</v>
+        <v>246</v>
       </c>
       <c r="F18" t="n">
-        <v>599</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30814</v>
+        <v>109440</v>
       </c>
       <c r="D19" t="n">
-        <v>1436</v>
+        <v>2676</v>
       </c>
       <c r="E19" t="n">
-        <v>343</v>
+        <v>424</v>
       </c>
       <c r="F19" t="n">
-        <v>217</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>178125</v>
+        <v>439416</v>
       </c>
       <c r="D20" t="n">
-        <v>3070</v>
+        <v>5320</v>
       </c>
       <c r="E20" t="n">
-        <v>300</v>
+        <v>755</v>
       </c>
       <c r="F20" t="n">
-        <v>149</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15500</v>
+        <v>10707</v>
       </c>
       <c r="D21" t="n">
-        <v>996</v>
+        <v>848</v>
       </c>
       <c r="E21" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,64 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37264</v>
+        <v>122455</v>
       </c>
       <c r="D22" t="n">
-        <v>1640</v>
+        <v>3032</v>
       </c>
       <c r="E22" t="n">
+        <v>538</v>
+      </c>
+      <c r="F22" t="n">
         <v>299</v>
       </c>
-      <c r="F22" t="n">
-        <v>287</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>346760</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5472</v>
+      </c>
+      <c r="E23" t="n">
+        <v>685</v>
+      </c>
+      <c r="F23" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15500</v>
+      </c>
+      <c r="D24" t="n">
+        <v>996</v>
+      </c>
+      <c r="E24" t="n">
+        <v>138</v>
+      </c>
+      <c r="F24" t="n">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14503.xlsx
+++ b/output/roomself_excel/14503.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>3504</v>
       </c>
-      <c r="E2" t="n">
-        <v>598</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>559</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>317</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>5601</v>
       </c>
-      <c r="E3" t="n">
-        <v>667</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>600</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>587</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +600,23 @@
       <c r="D4" t="n">
         <v>1648</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>142</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>40</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>1744</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>204</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>35</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>1232</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>133</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>36</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +699,38 @@
       <c r="D7" t="n">
         <v>3796</v>
       </c>
-      <c r="E7" t="n">
-        <v>295</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>260</v>
+        <v>40</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>103</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +748,15 @@
       <c r="D8" t="n">
         <v>2184</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +773,23 @@
       <c r="D9" t="n">
         <v>1436</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>195</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>40</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +806,31 @@
       <c r="D10" t="n">
         <v>1548</v>
       </c>
-      <c r="E10" t="n">
-        <v>323</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="G10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>102</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +847,15 @@
       <c r="D11" t="n">
         <v>2776</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +872,31 @@
       <c r="D12" t="n">
         <v>1640</v>
       </c>
-      <c r="E12" t="n">
-        <v>287</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>136</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +913,15 @@
       <c r="D13" t="n">
         <v>3070</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +938,23 @@
       <c r="D14" t="n">
         <v>2656</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>284</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>40</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +971,31 @@
       <c r="D15" t="n">
         <v>2668</v>
       </c>
-      <c r="E15" t="n">
-        <v>437</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>322</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>168</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +1012,38 @@
       <c r="D16" t="n">
         <v>4484</v>
       </c>
-      <c r="E16" t="n">
-        <v>586</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>439</v>
+        <v>287</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>514</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>404</v>
+      </c>
+      <c r="M16" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1061,23 @@
       <c r="D17" t="n">
         <v>2584</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>304</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>35</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1094,31 @@
       <c r="D18" t="n">
         <v>1764</v>
       </c>
-      <c r="E18" t="n">
-        <v>246</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>201</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G18" t="n">
+        <v>35</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>166</v>
+      </c>
+      <c r="J18" t="n">
+        <v>37</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1135,31 @@
       <c r="D19" t="n">
         <v>2676</v>
       </c>
-      <c r="E19" t="n">
-        <v>424</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>323</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>285</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1176,31 @@
       <c r="D20" t="n">
         <v>5320</v>
       </c>
-      <c r="E20" t="n">
-        <v>755</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>686</v>
-      </c>
+        <v>1436</v>
+      </c>
+      <c r="G20" t="n">
+        <v>37</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>612</v>
+      </c>
+      <c r="J20" t="n">
+        <v>37</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1217,15 @@
       <c r="D21" t="n">
         <v>848</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1242,31 @@
       <c r="D22" t="n">
         <v>3032</v>
       </c>
-      <c r="E22" t="n">
-        <v>538</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>299</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>499</v>
+      </c>
+      <c r="J22" t="n">
+        <v>40</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,11 +1283,38 @@
       <c r="D23" t="n">
         <v>5472</v>
       </c>
-      <c r="E23" t="n">
-        <v>685</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>599</v>
+        <v>551</v>
+      </c>
+      <c r="G23" t="n">
+        <v>32</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>267</v>
+      </c>
+      <c r="J23" t="n">
+        <v>37</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>616</v>
+      </c>
+      <c r="M23" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -959,12 +1332,31 @@
       <c r="D24" t="n">
         <v>996</v>
       </c>
-      <c r="E24" t="n">
-        <v>138</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>137</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>124</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/14503.xlsx
+++ b/output/roomself_excel/14503.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -543,6 +603,54 @@
       <c r="M2" t="n">
         <v>13</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>36</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>122</v>
+      </c>
+      <c r="U2" t="n">
+        <v>39</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -584,6 +692,54 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>291</v>
+      </c>
+      <c r="U3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>92</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +773,30 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +830,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>35</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -683,6 +887,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>36</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -732,6 +960,42 @@
       <c r="M7" t="n">
         <v>40</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>40</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -757,6 +1021,18 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -790,6 +1066,30 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -831,6 +1131,18 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -856,6 +1168,18 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -897,6 +1221,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -922,6 +1270,18 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -955,6 +1315,30 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>40</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -996,6 +1380,42 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>40</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>122</v>
+      </c>
+      <c r="U15" t="n">
+        <v>40</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1045,6 +1465,42 @@
       <c r="M16" t="n">
         <v>37</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>35</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>37</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1078,6 +1534,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1119,6 +1599,30 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>35</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1160,6 +1664,42 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>38</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>113</v>
+      </c>
+      <c r="U19" t="n">
+        <v>40</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1201,6 +1741,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1226,6 +1778,18 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1267,6 +1831,42 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>124</v>
+      </c>
+      <c r="U22" t="n">
+        <v>40</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1316,6 +1916,18 @@
       <c r="M23" t="n">
         <v>31</v>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1357,6 +1969,30 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>13</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
